--- a/base/StructureDefinition-SGMeasure.xlsx
+++ b/base/StructureDefinition-SGMeasure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="478">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mea-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}mea-1:Stratifier SHALL be either a single criteria or a set of criteria components {group.stratifier.all((code | description | criteria).exists() xor component.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mea-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}mea-1:Stratifier SHALL be either a single criteria or a set of criteria components {group.stratifier.all((code | description | criteria).exists() xor component.exists())}shr-1:If knowledge capabilities are stated, they SHALL include shareable {extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').exists() implies extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').where(value = 'shareable').exists()}</t>
   </si>
   <si>
     <t>Entity. Role, or Act</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -459,20 +459,8 @@
     <t>Defines a knowledge capability afforded by this knowledge artifact.</t>
   </si>
   <si>
-    <t>Measure.extension:artifactComment</t>
-  </si>
-  <si>
-    <t>artifactComment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {cqf-artifactComment}
-</t>
-  </si>
-  <si>
-    <t>Additional documentation, review, or usage guidance</t>
-  </si>
-  <si>
-    <t>A comment containing additional documentation, a review comment, usage guidance, or other relevant information from a particular user.</t>
+    <t>ele-1
+shr-1</t>
   </si>
   <si>
     <t>Measure.extension:versionAlgorithm</t>
@@ -494,6 +482,10 @@
     <t>If set as a string, this is a FHIRPath expression that has two additional context variables passed in - %version1 and %version2 and will return a negative number if version1 is newer, a positive number if version2 and a 0 if the version ordering can't be successfully be determined.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Measure.extension:versionPolicy</t>
   </si>
   <si>
@@ -508,6 +500,22 @@
   </si>
   <si>
     <t>Defines the versioning policy of the artifact.</t>
+  </si>
+  <si>
+    <t>Measure.extension:webSource</t>
+  </si>
+  <si>
+    <t>webSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {web-source}
+</t>
+  </si>
+  <si>
+    <t>web-source</t>
+  </si>
+  <si>
+    <t>Where a human readable web page describing the resource can be found, if it's at a different location to the canonical URL itself.</t>
   </si>
   <si>
     <t>Measure.modifierExtension</t>
@@ -699,7 +707,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>E.g. Patient, Practitioner, RelatedPerson, Organization, Location, Device</t>
@@ -720,7 +728,7 @@
     <t>The possible types of subjects for a measure (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Measure.date</t>
@@ -849,7 +857,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -978,7 +986,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.0.1</t>
   </si>
   <si>
     <t>Measure.author</t>
@@ -1045,7 +1053,7 @@
     <t>Measure.library</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Library)
+    <t xml:space="preserve">canonical(Library|4.0.1)
 </t>
   </si>
   <si>
@@ -1079,7 +1087,7 @@
     <t>The scoring type of the measure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-scoring</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-scoring|4.0.1</t>
   </si>
   <si>
     <t>Measure.compositeScoring</t>
@@ -1094,7 +1102,7 @@
     <t>The composite scoring method of the measure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/composite-measure-scoring</t>
+    <t>http://hl7.org/fhir/ValueSet/composite-measure-scoring|4.0.1</t>
   </si>
   <si>
     <t>Measure.type</t>
@@ -1109,7 +1117,7 @@
     <t>The type of measure (includes codes from 2.16.840.1.113883.1.11.20368).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-type</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-type|4.0.1</t>
   </si>
   <si>
     <t>Measure.riskAdjustment</t>
@@ -1304,7 +1312,7 @@
     <t>The type of population.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-population</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-population|4.0.1</t>
   </si>
   <si>
     <t>Measure.group.population.description</t>
@@ -1467,7 +1475,7 @@
     <t>The intended usage for supplemental data elements in the measure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-data-usage</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-data-usage|4.0.1</t>
   </si>
   <si>
     <t>Measure.supplementalData.description</t>
@@ -1805,17 +1813,17 @@
   <dimension ref="A1:AN88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.7578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.7578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.046875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="34.17578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="30.79296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1824,26 +1832,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="134.4609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.39453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.47265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="119.546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.5390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="86.95703125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="77.578125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2872,7 +2880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -2968,7 +2976,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>136</v>
@@ -2986,15 +2994,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -3004,7 +3012,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>86</v>
@@ -3016,15 +3024,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3082,7 +3092,7 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>136</v>
@@ -3102,13 +3112,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -3121,7 +3131,7 @@
         <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -3130,17 +3140,15 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3198,7 +3206,7 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>136</v>
@@ -3216,15 +3224,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -3246,13 +3254,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3312,7 +3320,7 @@
         <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>136</v>
@@ -3332,14 +3340,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3361,16 +3369,16 @@
         <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3419,7 +3427,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3446,12 +3454,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3477,16 +3485,16 @@
         <v>99</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3535,7 +3543,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3553,10 +3561,10 @@
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3564,10 +3572,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3590,19 +3598,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3651,7 +3659,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3669,21 +3677,21 @@
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3706,16 +3714,16 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3765,7 +3773,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3783,21 +3791,21 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3820,19 +3828,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3881,7 +3889,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3890,7 +3898,7 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>97</v>
@@ -3908,12 +3916,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3936,16 +3944,16 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3995,7 +4003,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4013,7 +4021,7 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -4024,10 +4032,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4050,13 +4058,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4107,7 +4115,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4134,12 +4142,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4165,13 +4173,13 @@
         <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4197,13 +4205,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4221,7 +4229,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4239,21 +4247,21 @@
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4276,19 +4284,19 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4337,7 +4345,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4355,10 +4363,10 @@
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4366,10 +4374,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4392,23 +4400,23 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="R23" t="s" s="2">
         <v>20</v>
@@ -4429,13 +4437,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4453,7 +4461,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4482,14 +4490,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4508,16 +4516,16 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4567,7 +4575,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4585,21 +4593,21 @@
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4622,19 +4630,19 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4683,7 +4691,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4701,10 +4709,10 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4712,10 +4720,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4738,16 +4746,16 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4797,7 +4805,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4815,7 +4823,7 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4824,12 +4832,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4852,16 +4860,16 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4911,7 +4919,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4929,7 +4937,7 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4940,10 +4948,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4966,19 +4974,19 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5027,7 +5035,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5045,7 +5053,7 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -5056,10 +5064,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5082,16 +5090,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5117,13 +5125,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5141,7 +5149,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5159,7 +5167,7 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5170,10 +5178,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5196,16 +5204,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5255,7 +5263,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5273,21 +5281,21 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5310,13 +5318,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5367,7 +5375,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5396,14 +5404,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5422,17 +5430,17 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5481,7 +5489,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5499,21 +5507,21 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5536,16 +5544,16 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5595,7 +5603,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5613,21 +5621,21 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5650,19 +5658,19 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5711,7 +5719,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5729,21 +5737,21 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5766,19 +5774,19 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5827,7 +5835,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5845,21 +5853,21 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5882,17 +5890,17 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5917,13 +5925,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5941,7 +5949,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5970,10 +5978,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5996,13 +6004,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6053,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6068,7 +6076,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6082,10 +6090,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6108,13 +6116,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6165,7 +6173,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6194,10 +6202,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6220,13 +6228,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6277,7 +6285,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6292,7 +6300,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6306,10 +6314,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6332,13 +6340,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6389,7 +6397,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6404,7 +6412,7 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6418,10 +6426,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6444,19 +6452,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6505,7 +6513,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6534,10 +6542,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6560,13 +6568,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6617,7 +6625,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6646,10 +6654,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6672,17 +6680,17 @@
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6731,7 +6739,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6760,10 +6768,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6786,13 +6794,13 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6819,13 +6827,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6843,7 +6851,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6872,10 +6880,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6898,13 +6906,13 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6931,13 +6939,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -6955,7 +6963,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6984,10 +6992,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7010,13 +7018,13 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7043,13 +7051,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7067,7 +7075,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7096,10 +7104,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7122,16 +7130,16 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7181,7 +7189,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7210,10 +7218,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7236,16 +7244,16 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7295,7 +7303,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7324,10 +7332,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7350,17 +7358,17 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7409,7 +7417,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7438,10 +7446,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7464,13 +7472,13 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7521,7 +7529,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7550,10 +7558,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7576,17 +7584,17 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7611,13 +7619,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7635,7 +7643,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7664,10 +7672,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7690,17 +7698,17 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7749,7 +7757,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7778,10 +7786,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7804,17 +7812,17 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7863,7 +7871,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7892,10 +7900,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7918,13 +7926,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7975,7 +7983,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8004,10 +8012,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8030,13 +8038,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8087,7 +8095,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8102,7 +8110,7 @@
         <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -8116,14 +8124,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8145,13 +8153,13 @@
         <v>130</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8201,7 +8209,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8216,7 +8224,7 @@
         <v>136</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>20</v>
@@ -8230,14 +8238,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8259,16 +8267,16 @@
         <v>130</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8317,7 +8325,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8346,10 +8354,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8372,13 +8380,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8429,7 +8437,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8458,10 +8466,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8484,13 +8492,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8541,7 +8549,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8570,10 +8578,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8596,13 +8604,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8653,7 +8661,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8682,10 +8690,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8708,13 +8716,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8765,7 +8773,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -8780,7 +8788,7 @@
         <v>20</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>20</v>
@@ -8794,14 +8802,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8823,13 +8831,13 @@
         <v>130</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8879,7 +8887,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -8894,7 +8902,7 @@
         <v>136</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
@@ -8908,14 +8916,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8937,16 +8945,16 @@
         <v>130</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -8995,7 +9003,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9024,10 +9032,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9050,13 +9058,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9083,13 +9091,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9107,7 +9115,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9136,10 +9144,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9162,13 +9170,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9219,7 +9227,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9248,10 +9256,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9274,16 +9282,16 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9333,7 +9341,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9362,10 +9370,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9388,13 +9396,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9445,7 +9453,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9474,10 +9482,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9500,13 +9508,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9557,7 +9565,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -9572,7 +9580,7 @@
         <v>20</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>20</v>
@@ -9586,14 +9594,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9615,13 +9623,13 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9671,7 +9679,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -9686,7 +9694,7 @@
         <v>136</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
@@ -9700,14 +9708,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9729,16 +9737,16 @@
         <v>130</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9787,7 +9795,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -9816,10 +9824,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9842,13 +9850,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9899,7 +9907,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -9928,10 +9936,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9954,13 +9962,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10011,7 +10019,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10040,10 +10048,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10066,13 +10074,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10123,7 +10131,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10152,10 +10160,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10178,16 +10186,16 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10237,7 +10245,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10266,10 +10274,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10292,13 +10300,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10349,7 +10357,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10364,7 +10372,7 @@
         <v>20</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>20</v>
@@ -10378,14 +10386,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10407,13 +10415,13 @@
         <v>130</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10463,7 +10471,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -10478,7 +10486,7 @@
         <v>136</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>20</v>
@@ -10492,14 +10500,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10521,16 +10529,16 @@
         <v>130</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -10579,7 +10587,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -10608,10 +10616,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10634,13 +10642,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10691,7 +10699,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -10720,10 +10728,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10746,13 +10754,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10803,7 +10811,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -10832,10 +10840,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10858,13 +10866,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10915,7 +10923,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -10944,10 +10952,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10970,16 +10978,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11029,7 +11037,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11058,10 +11066,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11084,13 +11092,13 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11141,7 +11149,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11156,7 +11164,7 @@
         <v>20</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>20</v>
@@ -11170,14 +11178,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11199,13 +11207,13 @@
         <v>130</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11255,7 +11263,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -11270,7 +11278,7 @@
         <v>136</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>20</v>
@@ -11284,14 +11292,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11313,16 +11321,16 @@
         <v>130</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -11371,7 +11379,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -11400,10 +11408,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11426,13 +11434,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11483,7 +11491,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -11512,10 +11520,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11538,13 +11546,13 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11571,13 +11579,13 @@
         <v>20</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>20</v>
@@ -11595,7 +11603,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -11624,10 +11632,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11650,13 +11658,13 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11707,7 +11715,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -11736,10 +11744,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11762,13 +11770,13 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11819,7 +11827,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -11848,12 +11856,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN88">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
